--- a/projects/KE_Kapiti_Eddy_July/data/Exponential.decay.example.xlsx
+++ b/projects/KE_Kapiti_Eddy_July/data/Exponential.decay.example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hawkj\Documents\Github\L-DNDC\Landscape-DNDC\projects\KE_Kapiti_Eddy_July\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD18C3F-D8F6-4413-9721-7796F798D411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2241F70-F8F0-4ECD-A8CC-50AFB91B25BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" xr2:uid="{3C14AB75-1737-45B8-AA36-63A148897B83}"/>
+    <workbookView xWindow="-192" yWindow="-192" windowWidth="23424" windowHeight="12624" xr2:uid="{3C14AB75-1737-45B8-AA36-63A148897B83}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>k</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>Target SD as 'negligible'</t>
+  </si>
+  <si>
+    <t>Boma 2</t>
   </si>
 </sst>
 </file>
@@ -70,8 +73,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="0.000000"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -110,8 +113,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -446,34 +449,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFFCECA-6A94-4B3F-9B37-B48AB37117D9}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="11.20703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.20703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" t="s">
         <v>4</v>
       </c>
       <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <f>150*1.3</f>
-        <v>195</v>
+        <f>618</f>
+        <v>618</v>
       </c>
       <c r="C2">
-        <f>150*1.3</f>
-        <v>195</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>269.2</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -481,34 +490,44 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="C3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D3">
         <v>4.1999999999999997E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="C4">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>4000</v>
+      </c>
+      <c r="D4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="1">
         <f>B2*2.71828^(-B3*B4)</f>
-        <v>0.48335862524096146</v>
+        <v>3.7971538842237027E-3</v>
       </c>
       <c r="C6" s="1">
         <f>C2*2.71828^(-C3*C4)</f>
-        <v>0.35808094896140025</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>1.654035316558286E-3</v>
+      </c>
+      <c r="D6" s="1">
+        <f>D2*2.71828^(-D3*D4)</f>
+        <v>2.5282942451614603E-6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -518,18 +537,25 @@
       <c r="C8">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D8">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="2">
         <f>-LN(B8/B2)/B4</f>
-        <v>3.7877923257788964E-3</v>
+        <v>2.1822683876129342E-3</v>
       </c>
       <c r="C10" s="2">
         <f>-LN(C8/C2)/C4</f>
-        <v>5.0503897677051952E-3</v>
+        <v>1.9745099226911545E-3</v>
+      </c>
+      <c r="D10" s="2">
+        <f>-LN(D8/D2)/D4</f>
+        <v>2.704944571102571E-3</v>
       </c>
     </row>
   </sheetData>
